--- a/artfynd/A 36160-2025 artfynd.xlsx
+++ b/artfynd/A 36160-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17279503</v>
+        <v>119628861</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,17 +710,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kulleråsberget, Mpd</t>
+          <t>Ã…s, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613739.2013893194</v>
+        <v>613739</v>
       </c>
       <c r="R2" t="n">
-        <v>6951641.42370659</v>
+        <v>6951747</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-10-15</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-10-15</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,39 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>119628860</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,122 +894,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>119628861</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>658</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ã…s, Mpd</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>613739</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6951747</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36160-2025 artfynd.xlsx
+++ b/artfynd/A 36160-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628861</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>